--- a/docs/StructureDefinition-BRAtestado.xlsx
+++ b/docs/StructureDefinition-BRAtestado.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-05T10:09:20-03:00</t>
+    <t>2026-06-16T17:47:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -506,7 +506,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -1138,7 +1138,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1216,7 +1216,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1301,7 +1301,7 @@
     <t>CarePlan.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1341,7 +1341,7 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1426,7 +1426,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1460,7 +1460,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1555,7 +1555,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1577,7 +1577,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
   </si>
   <si>
@@ -1667,7 +1667,7 @@
     <t>Identifies the results of the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1719,7 +1719,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|MedicationRequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
+    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
 </t>
   </si>
   <si>
@@ -1791,7 +1791,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1825,7 +1825,7 @@
     <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1852,7 +1852,7 @@
     <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1861,7 +1861,7 @@
     <t>CarePlan.activity.detail.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -2306,7 +2306,7 @@
     <t>Code for a known / defined timing pattern.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation</t>
+    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation|4.0.1</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -2318,7 +2318,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -2343,7 +2343,7 @@
     <t>CarePlan.activity.detail.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|RelatedPerson|Patient|CareTeam|HealthcareService|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|RelatedPerson|4.0.1|Patient|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -2369,7 +2369,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>What is to be administered/supplied</t>
@@ -2381,7 +2381,7 @@
     <t>A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -2397,7 +2397,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -6818,7 +6818,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>304</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>314</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>331</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>338</v>
       </c>
@@ -19124,12 +19124,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN143">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/docs/StructureDefinition-BRAtestado.xlsx
+++ b/docs/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRAtestado.xlsx
+++ b/docs/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRAtestado.xlsx
+++ b/docs/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRAtestado.xlsx
+++ b/docs/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
